--- a/docs/test-results/test-case-matrix-2026-09-12.xlsx
+++ b/docs/test-results/test-case-matrix-2026-09-12.xlsx
@@ -138,46 +138,58 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">已核实缺陷</t>
+          <t xml:space="preserve">已核实/已确认缺陷</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">待核实缺陷</t>
+          <t xml:space="preserve">其中已修复</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">数据来源</t>
+          <t xml:space="preserve">待核实缺陷</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">backend/src/main + frontend/src 全量扫描；5 路并行设计</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t xml:space="preserve">数据来源</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/src/main + frontend/src 全量扫描；5 路并行设计</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t xml:space="preserve">已知缺失</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">system/AI/前端模块未纳入（生成时 API 余额耗尽）</t>
         </is>
@@ -237,17 +249,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">文档停用在真实库上必然失败</t>
+          <t xml:space="preserve">文档停用在真实库上必然失败（已修复）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DocumentCommandService.disable:81 要求当前为 PUBLISHED,而 JdbcDocumentRepository:133 的 UPDATE 带 WHERE status='DRAFT' → 匹配 0 行抛 document_state_conflict。DocumentControllerTest 用内存替身(无此守卫)故为绿。</t>
+          <t xml:space="preserve">JdbcDocumentRepository 的两条 UPDATE 都带 status='DRAFT' 守卫(knowledge_document 与 document_version),而守卫比对的是库里存量行状态。因此 disable / applyAiCuratedMetadata / 发布指定版本 在真实库上匹配 0 行抛 document_state_conflict,即文档停用与 AI 编目应用不可用。测试全走内存替身故未发现。已于 e37ca49 删除两处守卫并补 H2 回归用例。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">已核实</t>
+          <t xml:space="preserve">已修复</t>
         </is>
       </c>
     </row>
@@ -458,12 +470,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">旧版本发布后仍为 PUBLISHED,与 javadoc「原版本转为历史」不符。</t>
+          <t xml:space="preserve">枚举声明 1 处、全仓库使用 0 处。旧版本发布后仍为 PUBLISHED,与 javadoc「原版本转为历史」不符;「哪些是历史版本」只能靠 document.current_version_id 反推。</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">待核实</t>
+          <t xml:space="preserve">已核实</t>
         </is>
       </c>
     </row>
@@ -490,7 +502,88 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">待核实</t>
+          <t xml:space="preserve">已核实</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">停用不可逆:资产与文档都没有恢复端点</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AssetStatus 只有 submit 与 disable 两条命令端点,DocumentStatus 只有 disable;找不到 /enable 或 /restore。一次误停用即永久退出业务、无法自救。业务已确认「停用应可逆」,本项按缺陷处理,待修复。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">业务已确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">停用文档可被普通 GET 直读,与检索排除不对称</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DocumentQueryService.getPublished:32-33 显式放行 DISABLED,但 searchPublished 排除它。若意图是「保留可追溯」,应明确谁可读、从哪读;现状是任何登录用户 GET /documents/{id} 即可取到停用文档。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已核实</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">错误码口径横向不统一,前端无法统一处理</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">资源不存在:资产/文档走 404,关联域走 422 invalid_request。乐观锁冲突:治理移交用 governance_state_conflict,执行/验收链用 governance_version_conflict。越权:部分 403 *_forbidden,部分 422。与 AGENTS.md「错误码全局唯一」规则冲突。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已核实</t>
         </is>
       </c>
     </row>

--- a/docs/test-results/test-case-matrix-2026-09-12.xlsx
+++ b/docs/test-results/test-case-matrix-2026-09-12.xlsx
@@ -6,6 +6,7 @@
     <sheet name="缺陷清单" sheetId="2" r:id="rId2"/>
     <sheet name="测试盲区" sheetId="3" r:id="rId3"/>
     <sheet name="全量用例" sheetId="4" r:id="rId4"/>
+    <sheet name="优先补齐清单" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -41161,4 +41162,2556 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用例编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">模块</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">用例标题</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">优先级</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-AI-038</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 建议</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已确认的建议再驳回</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-AI-040</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 建议</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">匿名确认在过滤器层被拒</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-AI-050</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 编目</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能力服务不可用返回 503 可用性错误</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-014</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">资产文件</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文件下载（preview 缺省）</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-018</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">资产文件</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fileId 不属于该资产</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-035</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">批量草稿</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">批次中一条编号冲突则整批不落库</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-045</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">资产提交</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提交前字段不齐</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-052</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">资产停用</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">草稿直接停用（非法流转）</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-058</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收藏</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">查询未收藏状态</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-069</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">评论</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内容与图片同时为空</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-082</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">评论图片</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">评论图片读取</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-083</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">评论图片</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未关联该资产的图片 key</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-084</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">评论删除</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">删除本人评论</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-085</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">评论删除</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">删除他人评论且无审核角色</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-ASSET-093</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">评论点赞</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对已删除评论点赞（非法流转）</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-010</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文档域</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">匿名写请求被会话过滤器拦截为 401 auth_failed</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文档域</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">草稿文档不能创建新版本（非法流转）</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-030</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文档域</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">重复发布同一版本被拒（旧版本回炉）</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-032</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文档域</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已停用文档不能发布新版本（非法流转）</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-036</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文档域</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">草稿直接停用被拒（非法流转）</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-042</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文件访问</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">草稿文档的文件不可通过公开路由读取</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-048</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文档协作</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对草稿或不存在文档收藏返回 404</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-049</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文档协作</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">匿名收藏/取消收藏被拦截为 401</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-057</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文档协作</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">评论缺少版本或内容为空时被校验拦截</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-062</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文档协作</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">取消点赞后计数回落</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-068</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">文档协作</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">匿名点赞/删除评论被拦截为 401</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-077</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字典域</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同分类下字典编码重复被拒</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-084</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字典域</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已合并字典项不可再编辑（终端状态）</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-090</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">字典域</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合并目标非启用或源项有启用子项时被拒</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-098</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">资产文档关联</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">关联不存在的资产被拒</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-099</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">资产文档关联</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">关联已停用文档被拒、草稿文档可关联</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-100</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">资产文档关联</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">匿名建立关联被拦截为 401</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-DOC-108</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">资产文档关联</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">目标关系类型已存在时拒绝改类型</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-011</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">任务</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已完成任务禁止移交</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-038</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">任务</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">草稿任务直接送确认</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-048</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">确认</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">非 0 的 decisionVersion</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-056</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">确认</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">陈旧 roundVersion 完成轮次（并发双完）</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-058</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">确认</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">任务不在待确认状态时完成轮次</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-062</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">验收</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">任务不在待验收状态读取验收轮次</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-063</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">验收</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无治理管理角色读取验收轮次</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-068</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">验收</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轮次完成后继续保存样本</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-073</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">验收</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">陈旧 roundVersion 完成验收（并发双完）</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-075</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">验收</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">任务不在待验收状态完成验收</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-078</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">验收</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无管理角色完成验收</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-080</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">返工</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">任务不在待返工状态开启返工</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-081</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">返工</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">陈旧 taskVersion 开启返工</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-084</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">返工</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无管理角色开启返工</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-094</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">执行</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已确认或已验收项保存草稿</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-100</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">执行</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">重复提交同一治理结果</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一致性</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-107</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">执行</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">批量 commands 为 null 或空数组</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-110</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">执行</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">批量提交含越权治理项</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-114</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">应用作业</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对成功作业重复重试</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOV-120</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">横切</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只读数据库配置下禁止治理写入</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-004</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">查询不存在的扫描运行</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-028</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapping</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新增映射规则版本使 ruleVersion 递增</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-032</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapping</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">查询不存在的映射规则</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-033</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapping</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">引用不存在的数据标准新建映射</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-034</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapping</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">引用的数据标准已停用时禁止新建映射（非法流转）</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-037</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapping</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同标准版本同 key 重复新建被拒</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-042</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapping</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">适用范围六元组不完整被拒</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-044</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapping</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">重复确认已确认映射被拒（非法流转）</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-046</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapping</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">停用未确认（草稿）映射被拒（非法流转）</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-060</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">查询标准影响评估清单</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-061</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">查询不存在的标准</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-067</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新版本号未高于源版本被拒</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-068</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对已启用标准重复启用被拒（非法流转）</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-069</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对已停用标准再次启用被拒（非法流转）</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-070</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对草稿标准执行停用被拒（非法流转）</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-071</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">standard</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">规则为空的草稿标准不能启用（非法流转）</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-081</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inventory</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">page 小于 1 被拒</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-082</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inventory</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_page 超出上限被拒</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-088</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">operations</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">开始日期晚于结束日期被拒</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-109</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">history</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">查询治理任务历史事件序列</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-110</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">history</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">查询治理任务报告</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-GOVB-111</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">history</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">查询不存在任务的报告</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-SYS-004</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">认证</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">登录入参空白触发 Bean Validation</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-SYS-011</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">认证</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">客户端自报身份头被会话身份覆写</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-SYS-012</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">认证</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">匿名写请求在过滤器层被拒</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-SYS-023</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系统管理</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">非管理员修改数据范围被拒</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-SYS-032</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">系统管理</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未登录修改用户角色被过滤器拦截</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-007</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-资料检索</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">首页资产列表加载与空态</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-008</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-资料检索</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">资产列表加载失败可重试</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-011</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-首页</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分数据源失败时降级提示</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-012</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-文档中心</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已发布文档列表与总数</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-016</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-上传</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">存在失败文件时禁止提交</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-017</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-上传</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提交成功提示与流转</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-019</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-我的收藏</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收藏列表渲染与取消收藏</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-029</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-AI 助手</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">重命名会话成功后列表刷新</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-031</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-AI 助手</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">删除会话需二次确认</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-035</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-AI 建议</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">非治理角色不显示操作按钮</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-037</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-AI 建议</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">确认时的越权或状态冲突错误提示</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">异常</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-041</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-系统管理</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">编辑权限保存成功并刷新</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">正向</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-UI-042</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">前端-系统管理</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">非管理员的权限修改被拒绝</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">权限</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>